--- a/DATABASE/products.xlsx
+++ b/DATABASE/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\GVX0EPF00029263\EXCELCNV\b8a5718b-c450-43f2-96b3-cb6640ca3546\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kacper\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{8DAEED91-0D2C-40FD-B7B2-B4A90784457B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24D913CF-809A-4A0C-A29B-381C8B9C9448}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CB2D66-8CBB-4AE8-8613-9FF48049E0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{BDDEF11D-48E2-485D-881C-A520722BAF6E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" xr2:uid="{BDDEF11D-48E2-485D-881C-A520722BAF6E}"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -36,25 +36,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>ID,PRODUCT,NO_PACKAGES_AVAILABLE,UPDATE</t>
+    <t>NAME</t>
   </si>
   <si>
-    <t>1,MILK,1200,2025-04-20</t>
+    <t>PRICE</t>
   </si>
   <si>
-    <t>2,BREAD,3168,2025-04-15</t>
+    <t>AMOUNT</t>
   </si>
   <si>
-    <t>3,BUTTER,336,2025-04-21</t>
+    <t>UPDATED</t>
+  </si>
+  <si>
+    <t>MILK</t>
+  </si>
+  <si>
+    <t>BREAD</t>
+  </si>
+  <si>
+    <t>BUTTER</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>2025-04-20</t>
+  </si>
+  <si>
+    <t>2025-04-15</t>
+  </si>
+  <si>
+    <t>2025-04-21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,8 +570,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% — akcent 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -610,9 +633,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -650,7 +673,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -756,7 +779,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -898,7 +921,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -906,34 +929,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BF3C97-3B39-463F-85EE-00AE7EEC71A8}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.3828125" customWidth="1"/>
+    <col min="3" max="3" width="19.69140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.3046875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="D2">
+        <v>500</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4">
         <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="D4">
+        <v>300</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>